--- a/artfynd/A 66111-2019 artfynd.xlsx
+++ b/artfynd/A 66111-2019 artfynd.xlsx
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126920468</v>
+        <v>126921758</v>
       </c>
       <c r="B2" t="n">
-        <v>78980</v>
+        <v>91480</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Pikku Pulinki öst, Nb</t>
+          <t>Pikku pulinki, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>888560</v>
+        <v>888577</v>
       </c>
       <c r="R2" t="n">
-        <v>7418157</v>
+        <v>7418138</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -776,45 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126921758</v>
+        <v>126920468</v>
       </c>
       <c r="B3" t="n">
-        <v>91406</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Pikku pulinki, Nb</t>
+          <t>Pikku Pulinki öst, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>888577</v>
+        <v>888560</v>
       </c>
       <c r="R3" t="n">
-        <v>7418138</v>
+        <v>7418157</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,12 +861,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -880,7 +880,7 @@
         <v>126921744</v>
       </c>
       <c r="B4" t="n">
-        <v>91699</v>
+        <v>91773</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126907614</v>
       </c>
       <c r="B5" t="n">
-        <v>97245</v>
+        <v>97320</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>126921750</v>
       </c>
       <c r="B6" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>126921771</v>
       </c>
       <c r="B7" t="n">
-        <v>91298</v>
+        <v>91372</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>126916787</v>
       </c>
       <c r="B8" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>126922262</v>
       </c>
       <c r="B9" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>126921889</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>126922263</v>
       </c>
       <c r="B11" t="n">
-        <v>91947</v>
+        <v>92021</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>126922273</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>126921844</v>
       </c>
       <c r="B13" t="n">
-        <v>75075</v>
+        <v>75135</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
